--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,6 +1001,223 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122753535</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106886</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klubberget S, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548114</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6517952</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122753534</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100520</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ålsjön Ö, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548185</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6518011</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>122753535</v>
       </c>
       <c r="B5" t="n">
-        <v>106886</v>
+        <v>106888</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>100520</v>
+        <v>100522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753535</v>
+        <v>122753534</v>
       </c>
       <c r="B5" t="n">
-        <v>106888</v>
+        <v>100530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Ålsjön Ö, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548114</v>
+        <v>548185</v>
       </c>
       <c r="R5" t="n">
-        <v>6517952</v>
+        <v>6518011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122753534</v>
+        <v>122753535</v>
       </c>
       <c r="B6" t="n">
-        <v>100522</v>
+        <v>106896</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1126,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1155,14 +1150,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålsjön Ö, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548185</v>
+        <v>548114</v>
       </c>
       <c r="R6" t="n">
-        <v>6518011</v>
+        <v>6517952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1190,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753534</v>
+        <v>122753535</v>
       </c>
       <c r="B5" t="n">
-        <v>100530</v>
+        <v>106896</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålsjön Ö, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548185</v>
+        <v>548114</v>
       </c>
       <c r="R5" t="n">
-        <v>6518011</v>
+        <v>6517952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122753535</v>
+        <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>106896</v>
+        <v>100530</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>245</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,14 +1155,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Ålsjön Ö, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548114</v>
+        <v>548185</v>
       </c>
       <c r="R6" t="n">
-        <v>6517952</v>
+        <v>6518011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1195,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>122753535</v>
       </c>
       <c r="B5" t="n">
-        <v>106896</v>
+        <v>106898</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>100530</v>
+        <v>100532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753535</v>
+        <v>122753534</v>
       </c>
       <c r="B5" t="n">
-        <v>106898</v>
+        <v>100540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Ålsjön Ö, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548114</v>
+        <v>548185</v>
       </c>
       <c r="R5" t="n">
-        <v>6517952</v>
+        <v>6518011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122753534</v>
+        <v>122753535</v>
       </c>
       <c r="B6" t="n">
-        <v>100532</v>
+        <v>106906</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1126,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1155,14 +1150,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålsjön Ö, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548185</v>
+        <v>548114</v>
       </c>
       <c r="R6" t="n">
-        <v>6518011</v>
+        <v>6517952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1190,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753534</v>
+        <v>122753535</v>
       </c>
       <c r="B5" t="n">
-        <v>100540</v>
+        <v>106906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålsjön Ö, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548185</v>
+        <v>548114</v>
       </c>
       <c r="R5" t="n">
-        <v>6518011</v>
+        <v>6517952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122753535</v>
+        <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>106906</v>
+        <v>100540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>245</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,14 +1155,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Ålsjön Ö, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548114</v>
+        <v>548185</v>
       </c>
       <c r="R6" t="n">
-        <v>6517952</v>
+        <v>6518011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1195,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753535</v>
+        <v>122753534</v>
       </c>
       <c r="B5" t="n">
-        <v>106906</v>
+        <v>100540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Ålsjön Ö, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548114</v>
+        <v>548185</v>
       </c>
       <c r="R5" t="n">
-        <v>6517952</v>
+        <v>6518011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122753534</v>
+        <v>122753535</v>
       </c>
       <c r="B6" t="n">
-        <v>100540</v>
+        <v>106906</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1126,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1155,14 +1150,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålsjön Ö, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548185</v>
+        <v>548114</v>
       </c>
       <c r="R6" t="n">
-        <v>6518011</v>
+        <v>6517952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1190,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753534</v>
+        <v>122753535</v>
       </c>
       <c r="B5" t="n">
-        <v>100540</v>
+        <v>106909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålsjön Ö, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548185</v>
+        <v>548114</v>
       </c>
       <c r="R5" t="n">
-        <v>6518011</v>
+        <v>6517952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122753535</v>
+        <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>106906</v>
+        <v>100543</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>245</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,14 +1155,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Ålsjön Ö, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548114</v>
+        <v>548185</v>
       </c>
       <c r="R6" t="n">
-        <v>6517952</v>
+        <v>6518011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1195,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>122753535</v>
       </c>
       <c r="B5" t="n">
-        <v>106909</v>
+        <v>106911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>100543</v>
+        <v>100545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88406</v>
+        <v>88409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88406</v>
+        <v>88409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88406</v>
+        <v>88409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88409</v>
+        <v>88415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88409</v>
+        <v>88415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88409</v>
+        <v>88415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88415</v>
+        <v>88423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88415</v>
+        <v>88423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88415</v>
+        <v>88423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88423</v>
+        <v>88424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88423</v>
+        <v>88424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88423</v>
+        <v>88424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88424</v>
+        <v>88425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88424</v>
+        <v>88425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88424</v>
+        <v>88425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88425</v>
+        <v>88427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88425</v>
+        <v>88427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88425</v>
+        <v>88427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680733</v>
       </c>
       <c r="B2" t="n">
-        <v>88427</v>
+        <v>88428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88427</v>
+        <v>88428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88427</v>
+        <v>88428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680733</v>
+        <v>122753535</v>
       </c>
       <c r="B2" t="n">
-        <v>88431</v>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1008</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorps naturreservat, Ög</t>
+          <t>Klubberget S, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548167</v>
+        <v>548114</v>
       </c>
       <c r="R2" t="n">
-        <v>6518006</v>
+        <v>6517952</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +748,11 @@
           <t>2023-08-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -758,11 +763,6 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -784,7 +784,7 @@
         <v>113680731</v>
       </c>
       <c r="B3" t="n">
-        <v>88431</v>
+        <v>88486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113680732</v>
       </c>
       <c r="B4" t="n">
-        <v>88431</v>
+        <v>88486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,50 +993,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753535</v>
+        <v>113680733</v>
       </c>
       <c r="B5" t="n">
-        <v>106911</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>1008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klubberget S, Ög</t>
+          <t>Tjuttorps naturreservat, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548114</v>
+        <v>548167</v>
       </c>
       <c r="R5" t="n">
-        <v>6517952</v>
+        <v>6518006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1066,6 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>7 plantor. Överblommade. Växer i dikeskanten.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1086,6 +1076,11 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1107,12 +1102,7 @@
         <v>122753534</v>
       </c>
       <c r="B6" t="n">
-        <v>100545</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1194,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 50904-2024 artfynd.xlsx
+++ b/artfynd/A 50904-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680731</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680732</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680733</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>